--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4510.16点（-0.84%），跌破20日均线；两市成交额约19719亿元，较前5日均量放大（前5日均值约18880亿元），市场活跃度提升。</t>
+          <t>沪深300收于4510.16点（-0.84%），跌破20日均线；两市成交额约19719亿元（前5日均量口径暂缺，未做量能对比）。</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4510.16点（-0.84%），跌破20日均线；两市成交额约19719亿元（前5日均量口径暂缺，未做量能对比）。</t>
+          <t>沪深300收于4510.16点（-0.84%），跌破20日均线；两市成交额约19719亿元，较前5日均量放大（前5日均值约18880亿元），市场活跃度提升。</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -810,6 +810,58 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>3885.33（-0.07%）</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13384.57（-0.64%）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4480.08（-0.67%）</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16292亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>医疗研发外包(5.75%)、胶黏剂及胶带(4.44%)、医疗服务(4.09%)、诊断服务(4.03%)、横向通用软件(3.96%)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>教育运营及其他(-7.9%)、其他种植业(-6.04%)、粮食种植(-5.87%)、种植业(-4.18%)、人工景区(-3.71%)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4480.08点（-0.67%），跌破20日均线；两市成交额约16292亿元，较前5日均量萎缩（前5日均值约18762亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为医疗研发外包、胶黏剂及胶带、医疗服务，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -862,6 +862,58 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>3864.28（-0.54%）</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>13287.97（-0.72%）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4450.04（-0.67%）</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16127亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>钨(5.88%)、风电零部件(4.78%)、风电设备(4.2%)、教育运营及其他(2.88%)、半导体设备(2.86%)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>种子(-6.93%)、其他种植业(-6.64%)、百货(-6.15%)、种植业(-6.01%)、超市(-5.75%)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4450.04点（-0.67%），跌破20日均线；两市成交额约16127亿元，较前5日均量萎缩（前5日均值约18128亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为钨、风电零部件、风电设备，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -914,6 +914,58 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>3891.60（+0.71%）</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13454.74（+1.26%）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4480.27（+0.68%）</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18391亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>运动服装(7.34%)、炭黑(6.75%)、半导体材料(6.14%)、林业Ⅲ(5.97%)、林业Ⅱ(5.97%)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>商用载客车(-2.62%)、生猪养殖(-2.38%)、涂料(-1.96%)、风电整机(-1.84%)、商用车(-1.72%)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4480.27点（+0.68%），跌破20日均线；两市成交额约18391亿元，较前5日均量放大（前5日均值约17433亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为运动服装、炭黑、半导体材料，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -914,58 +914,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>3891.60（+0.71%）</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13454.74（+1.26%）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4480.27（+0.68%）</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18391亿元（沪+深）</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>运动服装(7.34%)、炭黑(6.75%)、半导体材料(6.14%)、林业Ⅲ(5.97%)、林业Ⅱ(5.97%)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>商用载客车(-2.62%)、生猪养殖(-2.38%)、涂料(-1.96%)、风电整机(-1.84%)、商用车(-1.72%)</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>沪深300收于4480.27点（+0.68%），跌破20日均线；两市成交额约18391亿元，较前5日均量放大（前5日均值约17433亿元），市场活跃度提升。</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>当日领涨板块为运动服装、炭黑、半导体材料，与观察池重合度低，维持现有组合，等待评分触发。</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -966,6 +966,58 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>3875.60（-0.41%）</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>13409.91（-0.33%）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4460.16（-0.45%）</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18231亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>种子(7.86%)、视频媒体(6.58%)、房产租赁经纪(5.28%)、其他养殖(5.13%)、种植业(5.06%)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>白银(-6.0%)、贵金属(-5.35%)、黄金(-5.15%)、电能综合服务(-2.65%)、稀土(-2.6%)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4460.16点（-0.45%），跌破20日均线；两市成交额约18231亿元，较前5日均量放大（前5日均值约17400亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为种子、视频媒体、房产租赁经纪，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13454.74（+1.26%）</t>
+          <t>13467.07（+1.35%）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18391亿元（沪+深）</t>
+          <t>16343亿元（沪+深）</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4480.27点（+0.68%），跌破20日均线；两市成交额约18391亿元，较前5日均量放大（前5日均值约17433亿元），市场活跃度提升。</t>
+          <t>沪深300收于4480.27点（+0.68%），跌破20日均线；两市成交额约16343亿元，较前5日均量萎缩（前5日均值约17433亿元），市场情绪偏谨慎。</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1018,6 +1018,58 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>3911.87（+0.94%）</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13640.87（+1.72%）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4507.39（+1.06%）</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20771亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>其他医疗服务(6.72%)、房产租赁经纪(4.86%)、半导体设备(4.83%)、数字芯片设计(4.68%)、集成电路制造(4.59%)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>其他养殖(-3.47%)、种子(-1.52%)、涂料(-1.51%)、汽车经销商(-1.49%)、汽车服务(-1.11%)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4507.39点（+1.06%），跌破20日均线；两市成交额约20771亿元，较前5日均量放大（前5日均值约17752亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为其他医疗服务、房产租赁经纪、半导体设备，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1070,58 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>3949.91（+0.97%）</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13730.02（+0.65%）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4539.57（+0.71%）</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20315亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>其他医疗服务(7.97%)、房产租赁经纪(7.35%)、会展服务(7.18%)、宠物食品(6.61%)、防水材料(6.14%)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>空调(-2.12%)、黄金(-1.51%)、贵金属(-1.51%)、白银(-1.5%)、钨(-0.98%)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4539.57点（+0.71%），跌破20日均线；两市成交额约20315亿元，较前5日均量放大（前5日均值约17962亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为其他医疗服务、房产租赁经纪、会展服务，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1122,6 +1122,58 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>3952.13（+0.06%）</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>13723.74（-0.05%）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4544.59（+0.11%）</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21356亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>燃料电池(10.78%)、其他家电Ⅲ(5.0%)、其他家电Ⅱ(5.0%)、广告媒体(4.2%)、教育出版(3.77%)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>涂料(-5.79%)、橡胶助剂(-2.82%)、旅游综合(-2.62%)、快递(-2.51%)、航运(-2.38%)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4544.59点（+0.11%），跌破20日均线；两市成交额约21356亿元，较前5日均量放大（前5日均值约18767亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为燃料电池、其他家电Ⅲ、其他家电Ⅱ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1174,6 +1174,58 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>3936.52（-0.39%）</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13636.07（-0.64%）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4517.28（-0.60%）</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17650亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>半导体材料(3.8%)、房产租赁经纪(3.21%)、光伏加工设备(2.82%)、仪器仪表(2.79%)、有机硅(2.69%)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>焦炭Ⅱ(-5.09%)、焦炭Ⅲ(-5.09%)、文字媒体(-5.0%)、其他养殖(-4.85%)、教育运营及其他(-4.82%)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4517.28点（-0.60%），跌破20日均线；两市成交额约17650亿元，较前5日均量萎缩（前5日均值约19813亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为半导体材料、房产租赁经纪、光伏加工设备，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1226,6 +1226,58 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>3888.37（-1.22%）</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13316.97（-2.34%）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4439.14（-1.73%）</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16534亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>半导体材料(3.8%)、房产租赁经纪(3.21%)、光伏加工设备(2.82%)、仪器仪表(2.79%)、有机硅(2.69%)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>广告媒体(-4.2%)、印制电路板(-4.04%)、白银(-3.98%)、贵金属(-3.84%)、黄金(-3.8%)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4439.14点（-1.73%），跌破20日均线；两市成交额约16534亿元，较前5日均量萎缩（前5日均值约19665亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为半导体材料、房产租赁经纪、光伏加工设备，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>沪深300单日跌幅超1.5%，警惕系统性回调，必要时降低仓位；个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -1254,12 +1254,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>半导体材料(3.8%)、房产租赁经纪(3.21%)、光伏加工设备(2.82%)、仪器仪表(2.79%)、有机硅(2.69%)</t>
+          <t>林业Ⅲ(5.83%)、林业Ⅱ(5.83%)、其他医疗服务(4.29%)、其他家电Ⅲ(4.24%)、其他家电Ⅱ(4.24%)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>广告媒体(-4.2%)、印制电路板(-4.04%)、白银(-3.98%)、贵金属(-3.84%)、黄金(-3.8%)</t>
+          <t>白银(-4.83%)、印制电路板(-4.74%)、广告媒体(-4.7%)、贵金属(-4.63%)、医疗研发外包(-4.61%)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>当日领涨板块为半导体材料、房产租赁经纪、光伏加工设备，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>当日领涨板块为林业Ⅲ、林业Ⅱ、其他医疗服务，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1278,6 +1278,58 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>3823.62（-1.67%）</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12858.75（-3.44%）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4340.76（-2.22%）</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17028亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>林业Ⅲ(5.83%)、林业Ⅱ(5.83%)、其他医疗服务(4.29%)、其他家电Ⅲ(4.24%)、其他家电Ⅱ(4.24%)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>白银(-4.83%)、印制电路板(-4.74%)、广告媒体(-4.7%)、贵金属(-4.63%)、医疗研发外包(-4.61%)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4340.76点（-2.22%），跌破20日均线；两市成交额约17028亿元，较前5日均量萎缩（前5日均值约19325亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为林业Ⅲ、林业Ⅱ、其他医疗服务，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>沪深300单日跌幅超1.5%，警惕系统性回调，必要时降低仓位；个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1330,6 +1330,58 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>3836.82（+0.35%）</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12924.31（+0.51%）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4352.79（+0.28%）</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11564亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>林业Ⅲ(5.83%)、林业Ⅱ(5.83%)、其他医疗服务(4.29%)、其他家电Ⅲ(4.24%)、其他家电Ⅱ(4.24%)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>白银(-4.83%)、印制电路板(-4.74%)、广告媒体(-4.7%)、贵金属(-4.63%)、医疗研发外包(-4.61%)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4352.79点（+0.28%），跌破20日均线；两市成交额约11564亿元，较前5日均量萎缩（前5日均值约18576亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为林业Ⅲ、林业Ⅱ、其他医疗服务，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>量能持续萎缩，反弹持续性存疑；个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -1338,22 +1338,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>3836.82（+0.35%）</t>
+          <t>3830.45（+0.18%）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12924.31（+0.51%）</t>
+          <t>12901.95（+0.34%）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4352.79（+0.28%）</t>
+          <t>4345.21（+0.10%）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11564亿元（沪+深）</t>
+          <t>14092亿元（沪+深）</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4352.79点（+0.28%），跌破20日均线；两市成交额约11564亿元，较前5日均量萎缩（前5日均值约18576亿元），市场情绪偏谨慎。</t>
+          <t>沪深300收于4345.21点（+0.10%），跌破20日均线；两市成交额约14092亿元，较前5日均量萎缩（前5日均值约18576亿元），市场情绪偏谨慎。</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1382,6 +1382,58 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>3842.19（+0.31%）</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>12887.62（-0.11%）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4357.62（+0.29%）</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14380亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>视频媒体(6.06%)、医美耗材(5.23%)、其他生物制品(4.72%)、疫苗(4.64%)、生物制品(4.53%)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>印制电路板(-4.56%)、集成电路封测(-4.1%)、元件(-4.01%)、集成电路制造(-3.58%)、半导体材料(-3.38%)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4357.62点（+0.29%），跌破20日均线；两市成交额约14380亿元，较前5日均量萎缩（前5日均值约17332亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为视频媒体、医美耗材、其他生物制品，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1434,6 +1434,58 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>3811.90（-0.79%）</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12620.90（-2.07%）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4310.28（-1.09%）</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16821亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>蓄电池及其他电池(5.19%)、锂电专用设备(4.98%)、焦炭Ⅲ(3.75%)、焦炭Ⅱ(3.75%)、油气及炼化工程(3.71%)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>视频媒体(-8.71%)、文字媒体(-7.95%)、分立器件(-6.36%)、集成电路制造(-5.52%)、模拟芯片设计(-5.4%)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4310.28点（-1.09%），跌破20日均线；两市成交额约16821亿元，较前5日均量放大（前5日均值约15937亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为蓄电池及其他电池、锂电专用设备、焦炭Ⅲ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1486,6 +1486,58 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>3819.04（+0.19%）</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>12654.02（+0.26%）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>4321.52（+0.26%）</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>18112亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>视频媒体(19.98%)、文字媒体(15.0%)、影视动漫制作(7.67%)、种子(7.44%)、影视院线(7.08%)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>印制电路板(-3.96%)、元件(-3.53%)、燃料电池(-3.44%)、风电零部件(-3.28%)、风电设备(-2.84%)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4321.52点（+0.26%），跌破20日均线；两市成交额约18112亿元，较前5日均量放大（前5日均值约15771亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为视频媒体、文字媒体、影视动漫制作，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -1494,42 +1494,42 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>3819.04（+0.19%）</t>
+          <t>3813.79（+0.05%）</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12654.02（+0.26%）</t>
+          <t>12641.86（+0.17%）</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4321.52（+0.26%）</t>
+          <t>4317.25（+0.16%）</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18112亿元（沪+深）</t>
+          <t>19006亿元（沪+深）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>视频媒体(19.98%)、文字媒体(15.0%)、影视动漫制作(7.67%)、种子(7.44%)、影视院线(7.08%)</t>
+          <t>视频媒体(19.98%)、文字媒体(15.0%)、种子(7.78%)、影视动漫制作(7.64%)、影视院线(7.06%)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>印制电路板(-3.96%)、元件(-3.53%)、燃料电池(-3.44%)、风电零部件(-3.28%)、风电设备(-2.84%)</t>
+          <t>印制电路板(-4.06%)、元件(-3.67%)、燃料电池(-3.34%)、风电零部件(-3.32%)、风电设备(-2.87%)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4321.52点（+0.26%），跌破20日均线；两市成交额约18112亿元，较前5日均量放大（前5日均值约15771亿元），市场活跃度提升。</t>
+          <t>沪深300收于4317.25点（+0.16%），跌破20日均线；两市成交额约19006亿元，较前5日均量放大（前5日均值约15771亿元），市场活跃度提升。</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>当日领涨板块为视频媒体、文字媒体、影视动漫制作，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>当日领涨板块为视频媒体、文字媒体、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1538,6 +1538,58 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>3797.24（-0.43%）</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>12384.87（-2.03%）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4287.98（-0.68%）</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15378亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>文字媒体(6.91%)、视频媒体(5.04%)、逆变器(4.42%)、影视动漫制作(4.24%)、大众出版(4.08%)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>房产租赁经纪(-6.61%)、种子(-6.41%)、白银(-5.93%)、锂(-5.44%)、氮肥(-5.29%)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4287.98点（-0.68%），跌破20日均线；两市成交额约15378亿元，较前5日均量萎缩（前5日均值约16265亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为文字媒体、视频媒体、逆变器，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1590,6 +1590,58 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>3800.86（+0.10%）</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12353.70（-0.25%）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4275.68（-0.29%）</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16759亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>其他数字媒体(11.94%)、印制电路板(6.08%)、纺织化学制品(5.43%)、元件(4.77%)、地面兵装Ⅲ(4.54%)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>锂电专用设备(-3.32%)、电池化学品(-3.14%)、保险Ⅱ(-3.12%)、保险Ⅲ(-3.12%)、逆变器(-2.99%)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4275.68点（-0.29%），跌破20日均线；两市成交额约16759亿元，较前5日均量放大（前5日均值约15935亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为其他数字媒体、印制电路板、纺织化学制品，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1642,6 +1642,58 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>3767.23（-0.88%）</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>12110.59（-1.97%）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4217.68（-1.36%）</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14144亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>其他数字媒体(11.94%)、印制电路板(6.08%)、纺织化学制品(5.43%)、元件(4.77%)、地面兵装Ⅲ(4.54%)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>锂电专用设备(-3.32%)、电池化学品(-3.14%)、保险Ⅱ(-3.12%)、保险Ⅲ(-3.12%)、逆变器(-2.99%)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4217.68点（-1.36%），跌破20日均线；两市成交额约14144亿元，较前5日均量萎缩（前5日均值约16469亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为其他数字媒体、印制电路板、纺织化学制品，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -1670,12 +1670,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>其他数字媒体(11.94%)、印制电路板(6.08%)、纺织化学制品(5.43%)、元件(4.77%)、地面兵装Ⅲ(4.54%)</t>
+          <t>视频媒体(6.83%)、文字媒体(6.73%)、油气及炼化工程(3.01%)、油气开采Ⅲ(2.97%)、油气开采Ⅱ(2.97%)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>锂电专用设备(-3.32%)、电池化学品(-3.14%)、保险Ⅱ(-3.12%)、保险Ⅲ(-3.12%)、逆变器(-2.99%)</t>
+          <t>风电零部件(-5.92%)、金融信息服务(-5.75%)、风电设备(-5.74%)、镍(-5.4%)、锂电专用设备(-4.94%)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>当日领涨板块为其他数字媒体、印制电路板、纺织化学制品，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>当日领涨板块为视频媒体、文字媒体、油气及炼化工程，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1694,6 +1694,58 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>3707.48（-1.59%）</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>11816.79（-2.43%）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4166.01（-1.23%）</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>16330亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>卫浴电器(4.57%)、纺织鞋类制造(3.38%)、大众出版(1.37%)、电信运营商(1.11%)、白酒Ⅲ(1.03%)</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>金融信息服务(-6.85%)、焦炭Ⅱ(-6.46%)、焦炭Ⅲ(-6.46%)、其他数字媒体(-6.44%)、其他种植业(-6.28%)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4166.01点（-1.23%），跌破20日均线；两市成交额约16330亿元，较前5日均量萎缩（前5日均值约16422亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为卫浴电器、纺织鞋类制造、大众出版，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1746,6 +1746,58 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>3716.28（+0.24%）</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>11802.46（-0.12%）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4170.61（+0.11%）</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>15554亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>燃料电池(6.56%)、航空装备Ⅲ(5.98%)、航空装备Ⅱ(5.98%)、地面兵装Ⅲ(5.97%)、地面兵装Ⅱ(5.97%)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>文字媒体(-4.6%)、印制电路板(-4.51%)、蓄电池及其他电池(-4.19%)、视频媒体(-3.67%)、诊断服务(-3.61%)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4170.61点（+0.11%），跌破20日均线；两市成交额约15554亿元，较前5日均量萎缩（前5日均值约16323亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为燃料电池、航空装备Ⅲ、航空装备Ⅱ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1798,6 +1798,58 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>3730.92（+0.39%）</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>11817.42（+0.13%）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>4174.53（+0.09%）</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>14375亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>其他数字媒体(12.49%)、地面兵装Ⅲ(4.34%)、地面兵装Ⅱ(4.34%)、钾肥(3.39%)、厨房电器(3.35%)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>教育运营及其他(-6.78%)、其他种植业(-4.72%)、林业Ⅱ(-4.21%)、林业Ⅲ(-4.21%)、房地产综合服务(-4.09%)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4174.53点（+0.09%），跌破20日均线；两市成交额约14375亿元，较前5日均量萎缩（前5日均值约15633亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为其他数字媒体、地面兵装Ⅲ、地面兵装Ⅱ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1850,6 +1850,58 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>3735.37（+0.12%）</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>11801.29（-0.14%）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4152.11（-0.54%）</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>14561亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>其他数字媒体(12.49%)、地面兵装Ⅲ(4.34%)、地面兵装Ⅱ(4.34%)、钾肥(3.39%)、厨房电器(3.35%)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>教育运营及其他(-6.78%)、其他种植业(-4.72%)、林业Ⅱ(-4.21%)、林业Ⅲ(-4.21%)、房地产综合服务(-4.09%)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4152.11点（-0.54%），跌破20日均线；两市成交额约14561亿元，较前5日均量萎缩（前5日均值约15433亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为其他数字媒体、地面兵装Ⅲ、地面兵装Ⅱ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>其他数字媒体(12.49%)、地面兵装Ⅲ(4.34%)、地面兵装Ⅱ(4.34%)、钾肥(3.39%)、厨房电器(3.35%)</t>
+          <t>其他数字媒体(13.62%)、诊断服务(9.53%)、燃料电池(6.08%)、医美耗材(5.87%)、汽车综合服务(4.68%)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>教育运营及其他(-6.78%)、其他种植业(-4.72%)、林业Ⅱ(-4.21%)、林业Ⅲ(-4.21%)、房地产综合服务(-4.09%)</t>
+          <t>林业Ⅱ(-3.18%)、林业Ⅲ(-3.18%)、洗护用品(-2.9%)、航海装备Ⅱ(-2.9%)、航海装备Ⅲ(-2.9%)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>当日领涨板块为其他数字媒体、地面兵装Ⅲ、地面兵装Ⅱ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>当日领涨板块为其他数字媒体、诊断服务、燃料电池，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1902,6 +1902,58 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>3713.03（-0.60%）</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>11704.35（-0.82%）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4111.93（-0.97%）</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>14293亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>广告媒体(6.85%)、其他数字媒体(6.61%)、生猪养殖(3.79%)、电视广播Ⅲ(3.26%)、电视广播Ⅱ(3.26%)</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>电信运营商(-4.15%)、人力资源服务(-4.0%)、锂电池(-3.75%)、电池化学品(-3.46%)、电池(-3.33%)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4111.93点（-0.97%），跌破20日均线；两市成交额约14293亿元，较前5日均量萎缩（前5日均值约14993亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为广告媒体、其他数字媒体、生猪养殖，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1954,6 +1954,58 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>3658.03（-1.48%）</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>11357.32（-2.96%）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4036.30（-1.84%）</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>15287亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>电机Ⅲ(4.13%)、电机Ⅱ(4.13%)、医美耗材(2.35%)、医疗美容(1.71%)、电信运营商(1.18%)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>文字媒体(-7.15%)、影视动漫制作(-6.58%)、影视院线(-6.55%)、广告媒体(-6.52%)、院线(-6.46%)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4036.30点（-1.84%），跌破20日均线；两市成交额约15287亿元，较前5日均量放大（前5日均值约15023亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为电机Ⅲ、电机Ⅱ、医美耗材，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>沪深300单日跌幅超1.5%，警惕系统性回调，必要时降低仓位；个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2006,6 +2006,58 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>3690.48（+0.89%）</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>11673.83（+2.79%）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>4105.33（+1.71%）</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>19563亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>其他数字媒体(15.02%)、机器人(7.98%)、视频媒体(6.56%)、横向通用软件(5.72%)、医美服务(5.49%)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>国有大型银行Ⅲ(-2.75%)、食用菌(-2.6%)、水力发电(-1.87%)、油气及炼化工程(-0.83%)、其他石化(-0.8%)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4105.33点（+1.71%），跌破20日均线；两市成交额约19563亿元，较前5日均量放大（前5日均值约14814亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为其他数字媒体、机器人、视频媒体，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2058,6 +2058,58 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>3697.52（+0.19%）</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>11534.38（-1.19%）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>4103.54（-0.04%）</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>16088亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>会展服务(8.11%)、其他数字媒体(5.35%)、烘焙食品(4.72%)、视频媒体(4.0%)、学历教育(3.78%)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>印制电路板(-6.43%)、元件(-5.71%)、半导体设备(-5.41%)、通信线缆及配套(-5.35%)、集成电路封测(-5.06%)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4103.54点（-0.04%），跌破20日均线；两市成交额约16088亿元，较前5日均量放大（前5日均值约15616亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为会展服务、其他数字媒体、烘焙食品，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2110,6 +2110,58 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>3648.30（-1.33%）</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>11245.73（-2.50%）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>4049.55（-1.32%）</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>14610亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>会展服务(3.37%)、百货(2.42%)、粘胶(2.35%)、纺织鞋类制造(2.31%)、多业态零售(1.82%)</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>钴(-9.63%)、半导体设备(-6.32%)、防水材料(-6.31%)、诊断服务(-6.06%)、橡胶助剂(-6.01%)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4049.55点（-1.32%），跌破20日均线；两市成交额约14610亿元，较前5日均量萎缩（前5日均值约15959亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为会展服务、百货、粘胶，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2162,58 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>3681.47（+0.91%）</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>11473.18（+2.02%）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>4083.87（+0.85%）</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>16285亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>文字媒体(8.91%)、模拟芯片设计(6.07%)、航天装备Ⅲ(5.52%)、航天装备Ⅱ(5.52%)、医疗研发外包(5.4%)</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>白酒Ⅱ(-2.33%)、白酒Ⅲ(-2.33%)、涂料(-2.0%)、期货(-1.8%)、医美耗材(-1.64%)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4083.87点（+0.85%），跌破20日均线；两市成交额约16285亿元，较前5日均量放大（前5日均值约15968亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为文字媒体、模拟芯片设计、航天装备Ⅲ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2214,6 +2214,58 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>3651.43（-0.82%）</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>11138.20（-2.92%）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>4041.84（-1.03%）</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>15565亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>纺织鞋类制造(6.17%)、航天装备Ⅲ(3.88%)、航天装备Ⅱ(3.88%)、院线(3.29%)、核力发电(2.85%)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>印制电路板(-7.5%)、教育运营及其他(-6.71%)、元件(-6.42%)、通信线缆及配套(-6.34%)、通信网络设备及器件(-6.07%)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4041.84点（-1.03%），跌破20日均线；两市成交额约15565亿元，较前5日均量萎缩（前5日均值约16366亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为纺织鞋类制造、航天装备Ⅲ、航天装备Ⅱ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -2242,12 +2242,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>纺织鞋类制造(6.17%)、航天装备Ⅲ(3.88%)、航天装备Ⅱ(3.88%)、院线(3.29%)、核力发电(2.85%)</t>
+          <t>纺织鞋类制造(6.17%)、航天装备Ⅲ(3.54%)、航天装备Ⅱ(3.54%)、院线(3.37%)、核力发电(2.91%)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>印制电路板(-7.5%)、教育运营及其他(-6.71%)、元件(-6.42%)、通信线缆及配套(-6.34%)、通信网络设备及器件(-6.07%)</t>
+          <t>印制电路板(-7.97%)、通信线缆及配套(-7.01%)、元件(-6.99%)、通信网络设备及器件(-6.66%)、光学元件(-6.61%)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2266,6 +2266,58 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>3599.02（-1.44%）</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>10833.78（-2.73%）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3989.62（-1.29%）</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>14375亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>白酒Ⅲ(5.15%)、白酒Ⅱ(5.15%)、纺织鞋类制造(3.87%)、综合电商(3.51%)、医疗研发外包(3.37%)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>文字媒体(-9.9%)、其他数字媒体(-9.01%)、门户网站(-8.4%)、数字媒体(-8.36%)、钴(-8.14%)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于3989.62点（-1.29%），跌破20日均线；两市成交额约14375亿元，较前5日均量萎缩（前5日均值约16422亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为白酒Ⅲ、白酒Ⅱ、纺织鞋类制造，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/02_市场观察记录.xlsx
+++ b/outputs/02_市场观察记录.xlsx
@@ -2284,12 +2284,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3989.62（-1.29%）</t>
+          <t>3985.50（-1.39%）</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14375亿元（沪+深）</t>
+          <t>16745亿元（沪+深）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于3989.62点（-1.29%），跌破20日均线；两市成交额约14375亿元，较前5日均量萎缩（前5日均值约16422亿元），市场情绪偏谨慎。</t>
+          <t>沪深300收于3985.50点（-1.39%），跌破20日均线；两市成交额约16745亿元，较前5日均量放大（前5日均值约16422亿元），市场活跃度提升。</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
